--- a/InputData/trans/BSfVBP/BAU Subsidy for Vehicle Battery Production.xlsx
+++ b/InputData/trans/BSfVBP/BAU Subsidy for Vehicle Battery Production.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\BSfVBP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndiaEPS/Shared Documents/Completed EPS Variables/trans/BSfVBP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D16806-131B-4A2F-BC1B-5BA65B276163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{91D16806-131B-4A2F-BC1B-5BA65B276163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F58FCDC8-88C2-4FB8-B4C1-3302D0314B94}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="43095" yWindow="1080" windowWidth="14610" windowHeight="15585" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Sources:</t>
   </si>
@@ -54,26 +54,29 @@
     <t>2022 to 2012 USD</t>
   </si>
   <si>
-    <t>In the US, the Inflation Reduction Act includes a credit of $35/kWh for battery cells and $10/kWh for assembly for onroad vehicle</t>
-  </si>
-  <si>
-    <t>batteries.</t>
-  </si>
-  <si>
-    <t>United States Congress</t>
-  </si>
-  <si>
-    <t>H.R. 5376 - Inflation Reduction Act of 2022</t>
-  </si>
-  <si>
-    <t>https://www.congress.gov/bill/117th-congress/house-bill/5376/text</t>
+    <t>https://pib.gov.in/PressReleasePage.aspx?PRID=1945454#:~:text=The%20Government%20on%2012th%20May,cost%20reduction%20of%20electric%20vehicles.</t>
+  </si>
+  <si>
+    <t>Production Linked Incentive (PLI) Scheme for Advanced Chemistry Cells (ACC)</t>
+  </si>
+  <si>
+    <t>Ministry of Heavy Industries</t>
+  </si>
+  <si>
+    <t>https://www.livemint.com/auto-news/commercial-production-of-acc-batteries-under-pli-scheme-to-commence-from-fy24end-11692890717885.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Therefore we set all values to 0 for now </t>
+  </si>
+  <si>
+    <t>In India, the government has announced a subsidy (see above) for manufacturing of batteries - to be effective from end of FY 2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,6 +88,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -107,17 +118,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -134,9 +148,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -174,7 +188,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -280,7 +294,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -422,7 +436,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -430,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="101.28515625" customWidth="1"/>
@@ -451,17 +465,17 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>10</v>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -469,25 +483,34 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-    </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>0.78500000000000003</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" location=":~:text=The%20Government%20on%2012th%20May,cost%20reduction%20of%20electric%20vehicles." xr:uid="{6D1DA101-97C6-4E52-A229-675711A9835B}"/>
+    <hyperlink ref="A11" r:id="rId2" xr:uid="{D55627D8-2074-4504-A899-353E448A99DF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -497,10 +520,10 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -589,13 +612,95 @@
         <v>2048</v>
       </c>
       <c r="AD1">
+        <f>AC1 +1</f>
         <v>2049</v>
       </c>
       <c r="AE1">
+        <f>AD1 +1</f>
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF1">
+        <f t="shared" ref="AF1:AY1" si="0">AE1 +1</f>
+        <v>2051</v>
+      </c>
+      <c r="AG1">
+        <f t="shared" si="0"/>
+        <v>2052</v>
+      </c>
+      <c r="AH1">
+        <f t="shared" si="0"/>
+        <v>2053</v>
+      </c>
+      <c r="AI1">
+        <f t="shared" si="0"/>
+        <v>2054</v>
+      </c>
+      <c r="AJ1">
+        <f t="shared" si="0"/>
+        <v>2055</v>
+      </c>
+      <c r="AK1">
+        <f t="shared" si="0"/>
+        <v>2056</v>
+      </c>
+      <c r="AL1">
+        <f t="shared" si="0"/>
+        <v>2057</v>
+      </c>
+      <c r="AM1">
+        <f t="shared" si="0"/>
+        <v>2058</v>
+      </c>
+      <c r="AN1">
+        <f t="shared" si="0"/>
+        <v>2059</v>
+      </c>
+      <c r="AO1">
+        <f t="shared" si="0"/>
+        <v>2060</v>
+      </c>
+      <c r="AP1">
+        <f t="shared" si="0"/>
+        <v>2061</v>
+      </c>
+      <c r="AQ1">
+        <f t="shared" si="0"/>
+        <v>2062</v>
+      </c>
+      <c r="AR1">
+        <f t="shared" si="0"/>
+        <v>2063</v>
+      </c>
+      <c r="AS1">
+        <f t="shared" si="0"/>
+        <v>2064</v>
+      </c>
+      <c r="AT1">
+        <f t="shared" si="0"/>
+        <v>2065</v>
+      </c>
+      <c r="AU1">
+        <f t="shared" si="0"/>
+        <v>2066</v>
+      </c>
+      <c r="AV1">
+        <f t="shared" si="0"/>
+        <v>2067</v>
+      </c>
+      <c r="AW1">
+        <f t="shared" si="0"/>
+        <v>2068</v>
+      </c>
+      <c r="AX1">
+        <f t="shared" si="0"/>
+        <v>2069</v>
+      </c>
+      <c r="AY1">
+        <f t="shared" si="0"/>
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -606,44 +711,34 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -703,4 +798,184 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A36FA265-6560-4594-AF90-9E0A9901385B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBEAB837-343A-4311-962D-839E46E6E5BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAF9732B-C123-44D9-8672-85C26DD291EE}"/>
 </file>
--- a/InputData/trans/BSfVBP/BAU Subsidy for Vehicle Battery Production.xlsx
+++ b/InputData/trans/BSfVBP/BAU Subsidy for Vehicle Battery Production.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndiaEPS/Shared Documents/Completed EPS Variables/trans/BSfVBP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onewri-my.sharepoint.com/personal/anuj_talwar_wri_org/Documents/EPS/Transport/Input Data/Draft US 4.0/BSfVBP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{91D16806-131B-4A2F-BC1B-5BA65B276163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F58FCDC8-88C2-4FB8-B4C1-3302D0314B94}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{91D16806-131B-4A2F-BC1B-5BA65B276163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DED3F413-F8EB-4EE9-8425-87766F01B779}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="1080" windowWidth="14610" windowHeight="15585" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Sources:</t>
   </si>
@@ -52,6 +52,12 @@
   </si>
   <si>
     <t>2022 to 2012 USD</t>
+  </si>
+  <si>
+    <t>In the US, the Inflation Reduction Act includes a credit of $35/kWh for battery cells and $10/kWh for assembly for onroad vehicle</t>
+  </si>
+  <si>
+    <t>batteries.</t>
   </si>
   <si>
     <t>https://pib.gov.in/PressReleasePage.aspx?PRID=1945454#:~:text=The%20Government%20on%2012th%20May,cost%20reduction%20of%20electric%20vehicles.</t>
@@ -148,9 +154,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -188,7 +194,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -294,7 +300,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -436,7 +442,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -444,72 +450,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="101.28515625" customWidth="1"/>
+    <col min="2" max="2" width="101.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>2021</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>0.78500000000000003</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" location=":~:text=The%20Government%20on%2012th%20May,cost%20reduction%20of%20electric%20vehicles." xr:uid="{6D1DA101-97C6-4E52-A229-675711A9835B}"/>
-    <hyperlink ref="A11" r:id="rId2" xr:uid="{D55627D8-2074-4504-A899-353E448A99DF}"/>
+    <hyperlink ref="A12" r:id="rId2" xr:uid="{D55627D8-2074-4504-A899-353E448A99DF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -521,9 +537,9 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AY2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -620,7 +636,7 @@
         <v>2050</v>
       </c>
       <c r="AF1">
-        <f t="shared" ref="AF1:AY1" si="0">AE1 +1</f>
+        <f t="shared" ref="AF1:BB1" si="0">AE1 +1</f>
         <v>2051</v>
       </c>
       <c r="AG1">
@@ -700,7 +716,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -783,15 +799,6 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
         <v>0</v>
       </c>
     </row>
@@ -801,21 +808,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
     <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
@@ -959,23 +951,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B9DEA03-E1AA-4B99-8260-9B5639D77EDE}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBEAB837-343A-4311-962D-839E46E6E5BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A36FA265-6560-4594-AF90-9E0A9901385B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBEAB837-343A-4311-962D-839E46E6E5BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAF9732B-C123-44D9-8672-85C26DD291EE}"/>
 </file>